--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>120180.48</v>
+        <v>1686515.96</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,64 +1455,64 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-872775.61</v>
+        <v>120180.48</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,57 +1886,57 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1959561.32</v>
+        <v>-872775.61</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,72 +2302,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-2234532.01</v>
+        <v>-1959561.32</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>51740465.13511561</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-2234532.01</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>10419</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>51725137.17221419</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-1963222.49</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>4.537543108797375</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-26.15773787161569</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-3.820519029284098</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>10314</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
+          <t>-1123972.035583757</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1910683.74</v>
+        <v>-1963222.49</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>615.302</t>
+          <t>546.453</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-58.00</t>
+          <t>-42.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.04</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11560227.0</t>
+          <t>10394439.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>22381073.4</t>
+          <t>20006671.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18031481.2</t>
+          <t>18157534.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>24758190.76</t>
+          <t>24261717.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4349592</t>
+          <t>1849137</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-800598.7346591427</t>
+          <t>-971381.0430417393</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1365052.92</v>
+        <v>-1910683.74</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>841.387</t>
+          <t>615.302</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-30.15</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-72.53</t>
+          <t>-58.00</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.58</t>
+          <t>-110.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15676267.0</t>
+          <t>11560227.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24094268.6</t>
+          <t>22381073.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17698729.1</t>
+          <t>18031481.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>25054645.9</t>
+          <t>24758190.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6395539</t>
+          <t>4349592</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-697970.7010894471</t>
+          <t>-800598.7346591427</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-661734.29</v>
+        <v>-1365052.92</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>18.9</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>18.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1420.134</t>
+          <t>841.387</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-30.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-67.53</t>
+          <t>-72.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.03</t>
+          <t>-108.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26687469.0</t>
+          <t>15676267.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23608395.4</t>
+          <t>24094268.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18051820.7</t>
+          <t>17698729.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25477040.52</t>
+          <t>25054645.9</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5556574</t>
+          <t>6395539</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-704559.1400748366</t>
+          <t>-697970.7010894471</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-74364.3</v>
+        <v>-661734.29</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1881.849</t>
+          <t>1420.134</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.56</t>
+          <t>-67.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.84</t>
+          <t>-107.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35714954.0</t>
+          <t>26687469.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21031350.0</t>
+          <t>23608395.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17343118.9</t>
+          <t>18051820.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25994831.76</t>
+          <t>25477040.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3688231</t>
+          <t>5556574</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-819140.0198600123</t>
+          <t>-704559.1400748366</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-412380.1</v>
+        <v>-74364.3</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1152.713</t>
+          <t>1881.849</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.49</t>
+          <t>21.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-33.49</t>
+          <t>-57.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-105.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51725137.17221419</t>
+          <t>51740465.13511561</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22266450.0</t>
+          <t>35714954.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16308396.8</t>
+          <t>21031350.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21039695.6</t>
+          <t>17343118.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>27529893.78</t>
+          <t>25994831.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4731298</t>
+          <t>3688231</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-893096.3694619337</t>
+          <t>-819140.0198600123</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1847762.48</v>
+        <v>-412380.1</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>4.537543108797375</t>
+          <t>-24.01869676127416</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-26.15773787161569</t>
+          <t>-42.75264470335272</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3.820519029284098</t>
+          <t>-9.218241067287693</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,52 +1009,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1064,22 +1064,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1686515.96</v>
+        <v>1274712.79</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>120180.48</v>
+        <v>1686515.96</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,64 +1886,64 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-872775.61</v>
+        <v>120180.48</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,57 +2317,57 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1959561.32</v>
+        <v>-872775.61</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-2234532.01</v>
+        <v>-1959561.32</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,275 +3164,275 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>51713437.89177489</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-2234532.01</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>10157</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>51740465.13511561</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1963222.49</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>5.03</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>10419</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
+          <t>-1123972.035583757</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1910683.74</v>
+        <v>-1963222.49</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>615.302</t>
+          <t>546.453</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-58.00</t>
+          <t>-42.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.04</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11560227.0</t>
+          <t>10394439.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>22381073.4</t>
+          <t>20006671.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18031481.2</t>
+          <t>18157534.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>24758190.76</t>
+          <t>24261717.74</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4349592</t>
+          <t>1849137</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-800598.7346591427</t>
+          <t>-971381.0430417393</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1365052.92</v>
+        <v>-1910683.74</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>841.387</t>
+          <t>615.302</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-30.15</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-72.53</t>
+          <t>-58.00</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.58</t>
+          <t>-110.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15676267.0</t>
+          <t>11560227.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24094268.6</t>
+          <t>22381073.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17698729.1</t>
+          <t>18031481.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>25054645.9</t>
+          <t>24758190.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6395539</t>
+          <t>4349592</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-697970.7010894471</t>
+          <t>-800598.7346591427</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-661734.29</v>
+        <v>-1365052.92</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>18.9</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>18.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1420.134</t>
+          <t>841.387</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-30.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-67.53</t>
+          <t>-72.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.03</t>
+          <t>-108.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26687469.0</t>
+          <t>15676267.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23608395.4</t>
+          <t>24094268.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18051820.7</t>
+          <t>17698729.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25477040.52</t>
+          <t>25054645.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5556574</t>
+          <t>6395539</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-704559.1400748366</t>
+          <t>-697970.7010894471</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-74364.3</v>
+        <v>-661734.29</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1881.849</t>
+          <t>1420.134</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.65</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-57.56</t>
+          <t>-67.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.84</t>
+          <t>-107.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51740465.13511561</t>
+          <t>51713437.89177489</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35714954.0</t>
+          <t>26687469.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21031350.0</t>
+          <t>23608395.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17343118.9</t>
+          <t>18051820.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25994831.76</t>
+          <t>25477040.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3688231</t>
+          <t>5556574</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-819140.0198600123</t>
+          <t>-704559.1400748366</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-412380.1</v>
+        <v>-74364.3</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1274712.79</v>
+        <v>1209878.41</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,52 +1440,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1495,22 +1495,22 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1686515.96</v>
+        <v>1274712.79</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>120180.48</v>
+        <v>1686515.96</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,64 +2317,64 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-872775.61</v>
+        <v>120180.48</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,57 +2748,57 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1959561.32</v>
+        <v>-872775.61</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,72 +3164,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-2234532.01</v>
+        <v>-1959561.32</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,275 +3595,275 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>51693845.76008645</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-2234532.01</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>28.46</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>51713437.89177489</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1963222.49</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>10157</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
+          <t>-1123972.035583757</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1910683.74</v>
+        <v>-1963222.49</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>615.302</t>
+          <t>546.453</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-58.00</t>
+          <t>-42.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.04</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11560227.0</t>
+          <t>10394439.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>22381073.4</t>
+          <t>20006671.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18031481.2</t>
+          <t>18157534.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24758190.76</t>
+          <t>24261717.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4349592</t>
+          <t>1849137</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-800598.7346591427</t>
+          <t>-971381.0430417393</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1365052.92</v>
+        <v>-1910683.74</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>841.387</t>
+          <t>615.302</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.15</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-72.53</t>
+          <t>-58.00</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.58</t>
+          <t>-110.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15676267.0</t>
+          <t>11560227.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24094268.6</t>
+          <t>22381073.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17698729.1</t>
+          <t>18031481.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>25054645.9</t>
+          <t>24758190.76</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6395539</t>
+          <t>4349592</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-697970.7010894471</t>
+          <t>-800598.7346591427</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-661734.29</v>
+        <v>-1365052.92</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>18.9</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>18.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1420.134</t>
+          <t>841.387</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-30.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-67.53</t>
+          <t>-72.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.03</t>
+          <t>-108.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51713437.89177489</t>
+          <t>51693845.76008645</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26687469.0</t>
+          <t>15676267.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23608395.4</t>
+          <t>24094268.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18051820.7</t>
+          <t>17698729.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25477040.52</t>
+          <t>25054645.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5556574</t>
+          <t>6395539</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-704559.1400748366</t>
+          <t>-697970.7010894471</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-74364.3</v>
+        <v>-661734.29</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-14.84</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>29192637.8</t>
+          <t>26971384.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>21906077.96</t>
+          <t>21836585.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1209878.41</v>
+        <v>427399.3</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1274712.79</v>
+        <v>1209878.41</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,52 +1871,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1686515.96</v>
+        <v>1274712.79</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>120180.48</v>
+        <v>1686515.96</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,64 +2748,64 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-872775.61</v>
+        <v>120180.48</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,57 +3179,57 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1959561.32</v>
+        <v>-872775.61</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-2234532.01</v>
+        <v>-1959561.32</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>51653969.05683453</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2234532.01</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>28.82</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>10078</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>51693845.76008645</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1963222.49</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>5.29</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.46</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>9895</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
+          <t>-1123972.035583757</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1910683.74</v>
+        <v>-1963222.49</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>615.302</t>
+          <t>546.453</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-58.00</t>
+          <t>-42.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.04</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11560227.0</t>
+          <t>10394439.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22381073.4</t>
+          <t>20006671.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18031481.2</t>
+          <t>18157534.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24758190.76</t>
+          <t>24261717.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4349592</t>
+          <t>1849137</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-800598.7346591427</t>
+          <t>-971381.0430417393</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1365052.92</v>
+        <v>-1910683.74</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>841.387</t>
+          <t>615.302</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>24.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.15</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>840</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-72.53</t>
+          <t>-58.00</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.58</t>
+          <t>-110.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51693845.76008645</t>
+          <t>51653969.05683453</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15676267.0</t>
+          <t>11560227.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24094268.6</t>
+          <t>22381073.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17698729.1</t>
+          <t>18031481.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>25054645.9</t>
+          <t>24758190.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6395539</t>
+          <t>4349592</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-697970.7010894471</t>
+          <t>-800598.7346591427</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-661734.29</v>
+        <v>-1365052.92</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.84</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>18.9</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>18.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,72 +1014,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26971384.2</t>
+          <t>23879779.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>21836585.24</t>
+          <t>21839201.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>427399.3</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-72424.159683372</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-247016.0523772761</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>14439758</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-12.10</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-13.24</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>19.2</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,67 +1450,67 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1520,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29192637.8</t>
+          <t>26971384.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>21906077.96</t>
+          <t>21836585.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>1209878.41</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-40680.17919357124</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>427399.3038724996</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>15986358</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-13.70</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-12.10</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>19.45</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>1274712.79</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-125785.5397510387</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1209878.409091018</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>25410999</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-11.42</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,52 +2322,52 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2357,22 +2377,22 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>1686515.96</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-368633.5304495945</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1274712.794792797</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>22007057</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-9.13</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-11.42</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>120180.48</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-667423.7714027567</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>1686515.96026703</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>41554725</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-10.05</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-9.13</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,64 +3209,64 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-872775.61</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1095412.813524536</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>120180.4837921113</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>29897782</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-10.73</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-10.05</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,57 +3645,57 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,172 +3720,172 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1959561.32</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1316429.776673018</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-872775.6070217751</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>27092626</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-12.10</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-10.73</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
           <t>19.25</t>
@@ -3858,7 +3893,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3868,15 +3903,20 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,72 +4066,72 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-2234532.01</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1397094.171155062</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1959561.322219411</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>15821730</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-13.70</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-12.10</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>18.85</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,272 +4502,272 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>51610873.75215517</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-2234532.010993917</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>10368076</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>51653969.05683453</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-1963222.49</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>10078</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
           <t>18.85</t>
@@ -4730,15 +4775,20 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-1910683.74</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-1123972.035583757</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-1963222.494564854</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>14149582</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-13.24</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-13.93</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>615.302</t>
+          <t>546.453</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.12</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>757</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>16.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-58.00</t>
+          <t>-42.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.04</t>
+          <t>-111.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51653969.05683453</t>
+          <t>51610873.75215517</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11560227.0</t>
+          <t>10394439.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22381073.4</t>
+          <t>20006671.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18031481.2</t>
+          <t>18157534.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24758190.76</t>
+          <t>24261717.74</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4349592</t>
+          <t>1849137</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-800598.7346591427</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-1365052.92</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-971381.0430417393</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-1910683.73914602</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>10394439</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/18</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-13.70</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-13.24</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>9947</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,24 +1069,24 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23879779.4</t>
+          <t>24261943.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>21839201.36</t>
+          <t>22403454.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>14439758</v>
+        <v>43465545</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,72 +1450,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>26971384.2</t>
+          <t>23879779.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>21836585.24</t>
+          <t>21839201.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15986358</v>
+        <v>14439758</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,67 +1886,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29192637.8</t>
+          <t>26971384.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>21906077.96</t>
+          <t>21836585.24</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>25410999</v>
+        <v>15986358</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>22007057</v>
+        <v>25410999</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,52 +2758,52 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2813,22 +2813,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>41554725</v>
+        <v>22007057</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>29897782</v>
+        <v>41554725</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,64 +3645,64 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-872775.6070217751</t>
+          <t>120180.4837921113</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>27092626</v>
+        <v>29897782</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,57 +4081,57 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1959561.322219411</t>
+          <t>-872775.6070217751</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>15821730</v>
+        <v>27092626</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,72 +4502,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2234532.010993917</t>
+          <t>-1959561.322219411</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>10368076</v>
+        <v>15821730</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,280 +4938,280 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>51630367.93256815</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-2234532.010993917</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>10368076</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>10392</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>51610873.75215517</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-1963222.494564854</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>14149582</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>9947</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>546.453</t>
+          <t>755.064</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-29.40</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-35.40</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.24</t>
+          <t>-112.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51610873.75215517</t>
+          <t>51630367.93256815</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10394439.0</t>
+          <t>14149582.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20006671.2</t>
+          <t>15693596.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18157534.0</t>
+          <t>18362473.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24261717.74</t>
+          <t>23450677.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1849137</t>
+          <t>-2668876</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-971381.0430417393</t>
+          <t>-1123972.035583757</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1910683.73914602</t>
+          <t>-1963222.494564854</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>10394439</v>
+        <v>14149582</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24261943.4</t>
+          <t>25226666.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>22403454.84</t>
+          <t>22382197.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>43465545</v>
+        <v>26830670</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1505,24 +1505,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23879779.4</t>
+          <t>24261943.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>21839201.36</t>
+          <t>22403454.84</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>14439758</v>
+        <v>43465545</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26971384.2</t>
+          <t>23879779.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>21836585.24</t>
+          <t>21839201.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>15986358</v>
+        <v>14439758</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,67 +2322,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29192637.8</t>
+          <t>26971384.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>21906077.96</t>
+          <t>21836585.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>25410999</v>
+        <v>15986358</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>22007057</v>
+        <v>25410999</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,52 +3194,52 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>41554725</v>
+        <v>22007057</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>29897782</v>
+        <v>41554725</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,64 +4081,64 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-872775.6070217751</t>
+          <t>120180.4837921113</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>27092626</v>
+        <v>29897782</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,57 +4517,57 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1959561.322219411</t>
+          <t>-872775.6070217751</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>15821730</v>
+        <v>27092626</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,72 +4938,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51630367.93256815</t>
+          <t>51614057.95702006</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2234532.010993917</t>
+          <t>-1959561.322219411</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>10368076</v>
+        <v>15821730</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>755.064</t>
+          <t>547.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-31.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.40</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,280 +5374,280 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>26.91</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>19.52</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>51614057.95702006</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>10368076.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12429718.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>18019056.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>23072694.18</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-5589338</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-1294827.416416089</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-2234532.010993917</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>10368076</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>4.99</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>10497</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>19.05</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-3.57</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-35.40</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-112.33</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>51630367.93256815</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>14149582.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>15693596.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>18362473.4</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>23450677.48</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-2668876</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-1123972.035583757</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-1963222.494564854</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>14149582</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-13.93</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>5.04</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>10392</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>25226666.0</t>
+          <t>46668688.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>22382197.58</t>
+          <t>24467742.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>26830670</v>
+        <v>132621113</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,52 +1450,52 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>24261943.4</t>
+          <t>25226666.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>22403454.84</t>
+          <t>22382197.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>43465545</v>
+        <v>26830670</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,52 +1886,52 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23879779.4</t>
+          <t>24261943.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>21839201.36</t>
+          <t>22403454.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>14439758</v>
+        <v>43465545</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,72 +2322,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26971384.2</t>
+          <t>23879779.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>21836585.24</t>
+          <t>21839201.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>15986358</v>
+        <v>14439758</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29192637.8</t>
+          <t>26971384.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>21906077.96</t>
+          <t>21836585.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>25410999</v>
+        <v>15986358</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>19.61</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27274784.0</t>
+          <t>29192637.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>21873902.02</t>
+          <t>21906077.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>22007057</v>
+        <v>25410999</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,52 +3630,52 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.42</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3685,22 +3685,22 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24946987.8</t>
+          <t>27274784.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>22642043.72</t>
+          <t>21873902.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>41554725</v>
+        <v>22007057</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19465959.2</t>
+          <t>24946987.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>22577403.58</t>
+          <t>22642043.72</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>29897782</v>
+        <v>41554725</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,64 +4517,64 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>15565290.6</t>
+          <t>19465959.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>22772553.22</t>
+          <t>22577403.58</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-872775.6070217751</t>
+          <t>120180.4837921113</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>27092626</v>
+        <v>29897782</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,57 +4953,57 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.67</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12458810.8</t>
+          <t>15565290.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>22770756.54</t>
+          <t>22772553.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1959561.322219411</t>
+          <t>-872775.6070217751</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>15821730</v>
+        <v>27092626</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>547.7</t>
+          <t>827.243</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-31.02</t>
+          <t>-31.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,72 +5374,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-113.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51614057.95702006</t>
+          <t>51824812.76609442</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10368076.0</t>
+          <t>15821730.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12429718.2</t>
+          <t>12458810.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18019056.8</t>
+          <t>18276539.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>23072694.18</t>
+          <t>22770756.54</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5589338</t>
+          <t>-5817728</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1294827.416416089</t>
+          <t>-1397094.171155062</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2234532.010993917</t>
+          <t>-1959561.322219411</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>10368076</v>
+        <v>15821730</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>19.75</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>19.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>132621113.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>46668688.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>46668688.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>37930663.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>24467742.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>24467742.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>9216793.900870845</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>132621113</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>132621113.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>19.41</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>26830670.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>25226666.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>25226666</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>26250725.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>22382197.58</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>22382197.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1377500.007797588</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>26830670</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>26830670.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>19.28</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>43465545.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>24261943.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>24261943.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>24604465.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>22403454.84</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>22403454.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>1464002.624557309</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>43465545</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>43465545.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>14439758.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23879779.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23879779.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>21672869.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>21839201.36</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>21839201.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-247016.0523772761</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>14439758</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>14439758.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>15986358.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>26971384.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>26971384.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>21268337.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>21836585.24</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>21836585.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>427399.3038724996</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>15986358</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>15986358.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>19.49</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>25410999.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>29192637.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>29192637.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>20825724.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>21906077.96</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>21906077.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1209878.409091018</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>25410999</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>25410999.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>19.56</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22007057.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>27274784.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>27274784</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>19852251.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>21873902.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>21873902.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1274712.794792797</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22007057</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22007057.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>19.46</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>41554725.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>24946987.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>24946987.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>20320292.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>22642043.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>22642043.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1686515.96026703</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>41554725</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>41554725.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>29897782.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>19465959.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>19465959.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>19736315.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>22577403.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>22577403.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>120180.4837921113</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>29897782</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>29897782.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.45</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>27092626.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15565290.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>15565290.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>18973182.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>22772553.22</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>22772553.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-872775.6070217751</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>27092626</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>27092626.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>15821730.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>12458810.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>12458810.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>18276539.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>22770756.54</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>22770756.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1959561.322219411</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>15821730</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>15821730.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN4" t="n">
         <v>19.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,75 +2304,75 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN5" t="n">
         <v>19.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.31</v>
+        <v>19.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.6</v>
+        <v>19.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>26971384.2</v>
+        <v>23879779.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>21836585.24</v>
+        <v>21839201.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.61</v>
+        <v>19.6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>29192637.8</v>
+        <v>26971384.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>21906077.96</v>
+        <v>21836585.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.4</v>
+        <v>19.35</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.63</v>
+        <v>19.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>27274784</v>
+        <v>29192637.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>21873902.02</v>
+        <v>21906077.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.42</v>
+        <v>19.4</v>
       </c>
       <c r="AN9" t="n">
         <v>19.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>24946987.8</v>
+        <v>27274784</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>22642043.72</v>
+        <v>21873902.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.64</v>
+        <v>19.63</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>19465959.2</v>
+        <v>24946987.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>22577403.58</v>
+        <v>22642043.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,60 +4899,60 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.45</v>
+        <v>19.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.65</v>
+        <v>19.64</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15565290.6</v>
+        <v>19465959.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22772553.22</v>
+        <v>22577403.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-872775.6070217751</t>
+          <t>120180.4837921113</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>827.243</t>
+          <t>1390.52</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-31.83</t>
+          <t>-17.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-26.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,53 +5329,53 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.46</v>
+        <v>19.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.67</v>
+        <v>19.65</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>20.32</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.59</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51824812.76609442</t>
+          <t>51848508.62142856</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>12458810.8</v>
+        <v>15565290.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18276539.7</t>
+          <t>18973182.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22770756.54</v>
+        <v>22772553.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5817728</t>
+          <t>-3407891</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1397094.171155062</t>
+          <t>-1316429.776673018</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1959561.322219411</t>
+          <t>-872775.6070217751</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15821730.0</t>
+          <t>27092626.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-10.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>19.25</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN5" t="n">
         <v>19.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,70 +2739,70 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN6" t="n">
         <v>19.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,63 +3169,63 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.31</v>
+        <v>19.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.6</v>
+        <v>19.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>26971384.2</v>
+        <v>23879779.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>21836585.24</v>
+        <v>21839201.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,58 +3599,58 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.61</v>
+        <v>19.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>29192637.8</v>
+        <v>26971384.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>21906077.96</v>
+        <v>21836585.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.4</v>
+        <v>19.35</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.63</v>
+        <v>19.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>27274784</v>
+        <v>29192637.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21873902.02</v>
+        <v>21906077.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.42</v>
+        <v>19.4</v>
       </c>
       <c r="AN10" t="n">
         <v>19.63</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>24946987.8</v>
+        <v>27274784</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>22642043.72</v>
+        <v>21873902.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.64</v>
+        <v>19.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>19465959.2</v>
+        <v>24946987.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22577403.58</v>
+        <v>22642043.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1390.52</t>
+          <t>1511.061</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.96</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.78</t>
+          <t>-26.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,60 +5329,60 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.45</v>
+        <v>19.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.65</v>
+        <v>19.64</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.32</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.21</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-112.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51848508.62142856</t>
+          <t>51852131.41369472</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15565290.6</v>
+        <v>19465959.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18973182.0</t>
+          <t>19736315.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22772553.22</v>
+        <v>22577403.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3407891</t>
+          <t>-270356</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1316429.776673018</t>
+          <t>-1095412.813524536</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-872775.6070217751</t>
+          <t>120180.4837921113</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>27092626.0</t>
+          <t>29897782.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.73</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN6" t="n">
         <v>19.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,75 +3164,75 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN7" t="n">
         <v>19.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.31</v>
+        <v>19.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.6</v>
+        <v>19.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>26971384.2</v>
+        <v>23879779.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>21836585.24</v>
+        <v>21839201.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.61</v>
+        <v>19.6</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>29192637.8</v>
+        <v>26971384.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21906077.96</v>
+        <v>21836585.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.4</v>
+        <v>19.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.63</v>
+        <v>19.61</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>27274784</v>
+        <v>29192637.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>21873902.02</v>
+        <v>21906077.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.42</v>
+        <v>19.4</v>
       </c>
       <c r="AN11" t="n">
         <v>19.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24946987.8</v>
+        <v>27274784</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22642043.72</v>
+        <v>21873902.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1511.061</t>
+          <t>2059.606</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>22.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.22</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.64</v>
+        <v>19.63</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.44</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51852131.41369472</t>
+          <t>51960120.21794872</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>19465959.2</v>
+        <v>24946987.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19736315.2</t>
+          <t>20320292.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22577403.58</v>
+        <v>22642043.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-270356</t>
+          <t>4626695</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1095412.813524536</t>
+          <t>-667423.7714027567</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>120180.4837921113</t>
+          <t>1686515.96026703</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>29897782.0</t>
+          <t>41554725.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.05</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1781.106</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2221.352</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN7" t="n">
         <v>19.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,75 +3594,75 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN8" t="n">
         <v>19.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,68 +4024,68 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.31</v>
+        <v>19.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.6</v>
+        <v>19.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>26971384.2</v>
+        <v>23879779.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21836585.24</v>
+        <v>21839201.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.61</v>
+        <v>19.6</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>29192637.8</v>
+        <v>26971384.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>21906077.96</v>
+        <v>21836585.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.4</v>
+        <v>19.35</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.63</v>
+        <v>19.61</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>27274784</v>
+        <v>29192637.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>21873902.02</v>
+        <v>21906077.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2059.606</t>
+          <t>1113.079</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-27.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.13</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.42</v>
+        <v>19.4</v>
       </c>
       <c r="AN12" t="n">
         <v>19.63</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>48.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-109.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51960120.21794872</t>
+          <t>51955644.6251778</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24946987.8</v>
+        <v>27274784</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20320292.3</t>
+          <t>19852251.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22642043.72</v>
+        <v>21873902.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4626695</t>
+          <t>7422532</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-667423.7714027567</t>
+          <t>-368633.5304495945</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1686515.96026703</t>
+          <t>1274712.794792797</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>41554725.0</t>
+          <t>22007057.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,94 +993,94 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN8" t="n">
         <v>19.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,75 +4024,75 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN9" t="n">
         <v>19.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>840.246</t>
+          <t>757.102</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.90</t>
+          <t>-28.84</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>17.62</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.31</v>
+        <v>19.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.6</v>
+        <v>19.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>26971384.2</v>
+        <v>23879779.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21268337.4</t>
+          <t>21672869.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>21836585.24</v>
+        <v>21839201.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5703046</t>
+          <t>2206910</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-40680.17919357124</t>
+          <t>-72424.159683372</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>427399.3038724996</t>
+          <t>-247016.0523772761</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15986358.0</t>
+          <t>14439758.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1335.006</t>
+          <t>840.246</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-27.90</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.61</v>
+        <v>19.6</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.27</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>29192637.8</v>
+        <v>26971384.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20825724.3</t>
+          <t>21268337.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>21906077.96</v>
+        <v>21836585.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8366913</t>
+          <t>5703046</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-125785.5397510387</t>
+          <t>-40680.17919357124</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1209878.409091018</t>
+          <t>427399.3038724996</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>25410999.0</t>
+          <t>15986358.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1113.079</t>
+          <t>1335.006</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>40.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.34</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>84.13</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.4</v>
+        <v>19.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.63</v>
+        <v>19.61</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.85</t>
+          <t>-109.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51955644.6251778</t>
+          <t>51939020.07528409</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>27274784</v>
+        <v>29192637.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19852251.1</t>
+          <t>20825724.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>21873902.02</v>
+        <v>21906077.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7422532</t>
+          <t>8366913</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-368633.5304495945</t>
+          <t>-125785.5397510387</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1274712.794792797</t>
+          <t>1209878.409091018</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>22007057.0</t>
+          <t>25410999.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/08/18</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-7.35</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>2034</t>
@@ -879,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.18</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1665.664</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -924,37 +928,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-18 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-06 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-08 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-07-15 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -964,12 +968,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -979,160 +983,152 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>69.95</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.39</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>19.83</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>19.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>45.63</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.18</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51932456.60694051</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>42129365.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>28097779.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1142,17 +1138,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1197,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1207,90 +1203,4310 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1575.957</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-10.45</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-22.66</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>93.94</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>20.52</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.03</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>77.74</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-90.54</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>32455665.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>42639679.4</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>47616342.4</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>27712944.14</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-4976663</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>3855467.969003393</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2143172.30139979</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>32455665.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1314.256</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-23.60</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>84.85</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>93.94</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>103.71</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-92.38</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>26834641.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>45270134.6</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>45969411.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>27411404.62</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-699277</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>4166794.45402223</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>3470708.450914837</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>26834641.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>10811</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1580.465</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>44.95</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-22.85</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>96.97</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>93.11</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.54</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.07</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>168.05</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-94.35</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>32542519.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>66427429</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>45827047.5</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>27251457.28</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>20600381</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>4293355.545496301</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>5845487.362689376</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>32542519.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>20.85</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>20.45</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4087.718</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>45.81</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-22.66</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12.85</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>93.14</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-2.15</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.08</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>304.10</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-96.73</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>85106848.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>65285059.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>44773501.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>26980928.86</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>20511557</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>4011149.760552105</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>8417702.902271241</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>85106848.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>20.65</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1781.106</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>40.92</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-23.97</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>82.35</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>93.14</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-2.30</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>20.27</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>20.09</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1213.70</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-99.21</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>36258724.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>56956798.6</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>40418289.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>25505320.52</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>16538509</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>3209958.280239535</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>6159771.890878506</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>36258724.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2221.352</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-23.03</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6.98</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>97.06</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>632.62</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-101.60</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>45607941.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>52593005.4</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>39782194.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>25031853.16</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>12810810</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2673628.532850632</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>7947891.878500357</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>45607941.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>20.75</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>20.35</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6307.505</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>23.04</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-22.85</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19.83</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>98.33</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-2.58</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>211.54</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-104.12</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>132621113.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>46668688.8</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>37930663.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>24467742.9</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>8738025</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1714671.560914318</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>9216793.900870845</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>132621113.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1344.072</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-3.90</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-24.91</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>68.33</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-2.73</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>19.41</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>20.13</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-106.30</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>26830670.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>25226666</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>26250725.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>22382197.58</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-1024059</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>350649.3172858583</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1377500.007797588</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>26830670.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2188.924</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-25.66</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6.88</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>47.7</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-2.85</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>19.28</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-107.69</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>43465545.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>24261943.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>24604465.6</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>22403454.84</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-342522</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>163949.1917382712</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>1464002.624557309</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>43465545.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-2.70</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>20.25</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>19.85</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d1】;【d2】</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-1.3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>757.102</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10.18</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-28.84</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>19.29</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>20.17</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>10.62</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-108.54</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>51932456.60694051</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>14439758.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>23879779.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>21672869.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21839201.36</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>2206910</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-72424.159683372</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-247016.0523772761</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>14439758.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>19.45</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,168 +1014,168 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>51903364.22842998</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>51932456.60694051</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,38 +1837,38 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM4" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN4" t="n">
         <v>19.68</v>
       </c>
-      <c r="AN4" t="n">
-        <v>19.67</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,87 +2259,87 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,17 +3124,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.34</v>
+        <v>4.73</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.7</v>
+        <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.28</v>
+        <v>4.34</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.23</v>
+        <v>3.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.7</v>
+        <v>2.23</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN11" t="n">
         <v>19.58</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>757.102</t>
+          <t>2188.924</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.84</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,67 +5234,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.5</v>
+        <v>2.96</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.27</v>
+        <v>19.26</v>
       </c>
       <c r="AN12" t="n">
         <v>19.58</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.17</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="AQ12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AR12" t="n">
         <v>-0.13</v>
       </c>
-      <c r="AR12" t="n">
-        <v>-0.15</v>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-107.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51932456.60694051</t>
+          <t>51903364.22842998</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23879779.4</v>
+        <v>24261943.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21672869.3</t>
+          <t>24604465.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>21839201.36</v>
+        <v>22403454.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2206910</t>
+          <t>-342522</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-72424.159683372</t>
+          <t>163949.1917382712</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-247016.0523772761</t>
+          <t>1464002.624557309</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14439758.0</t>
+          <t>43465545.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AN2" t="n">
         <v>19.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AR2" t="n">
         <v>0.2</v>
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.83</v>
+        <v>19.89</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>22.89</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.32</t>
+          <t>-88.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33707156.0</t>
+          <t>20909430.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>42129365.8</v>
+        <v>29289882.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49543082.2</t>
+          <t>47287470.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>28097779.14</v>
+        <v>28319853.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-7413716</t>
+          <t>-17997588</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3455269.745188142</t>
+          <t>2868412.957514935</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1254179.514204264</t>
+          <t>-359299.3746877089</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>33707156.0</t>
+          <t>20909430.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,38 +2259,38 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM5" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN5" t="n">
         <v>19.68</v>
       </c>
-      <c r="AN5" t="n">
-        <v>19.67</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,87 +2681,87 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-4.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,17 +3546,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3565,47 +3565,47 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.34</v>
+        <v>4.73</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.7</v>
+        <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.28</v>
+        <v>4.34</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.23</v>
+        <v>3.28</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7</v>
+        <v>2.23</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2188.924</t>
+          <t>1344.072</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-24.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.26</v>
+        <v>19.27</v>
       </c>
       <c r="AN12" t="n">
         <v>19.58</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.69</t>
+          <t>-106.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51903364.22842998</t>
+          <t>51890827.53601695</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24261943.4</v>
+        <v>25226666</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24604465.6</t>
+          <t>26250725.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22403454.84</v>
+        <v>22382197.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-342522</t>
+          <t>-1024059</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>163949.1917382712</t>
+          <t>350649.3172858583</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1464002.624557309</t>
+          <t>1377500.007797588</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>43465545.0</t>
+          <t>26830670.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,243 +1029,243 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>51846104.14739069</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.06</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>30.17</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>10340</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>51890827.53601695</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>5.04</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>10392</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,48 +1451,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AN3" t="n">
         <v>19.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AR3" t="n">
         <v>0.2</v>
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.83</v>
+        <v>19.89</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>22.89</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.32</t>
+          <t>-88.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33707156.0</t>
+          <t>20909430.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>42129365.8</v>
+        <v>29289882.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49543082.2</t>
+          <t>47287470.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>28097779.14</v>
+        <v>28319853.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-7413716</t>
+          <t>-17997588</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3455269.745188142</t>
+          <t>2868412.957514935</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1254179.514204264</t>
+          <t>-359299.3746877089</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33707156.0</t>
+          <t>20909430.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,38 +2681,38 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM6" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN6" t="n">
         <v>19.68</v>
       </c>
-      <c r="AN6" t="n">
-        <v>19.67</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,87 +3103,87 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,17 +3968,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3987,47 +3987,47 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.34</v>
+        <v>4.73</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.7</v>
+        <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.28</v>
+        <v>4.34</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.23</v>
+        <v>3.28</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1344.072</t>
+          <t>6307.505</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.91</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.7</v>
+        <v>2.23</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>211.54</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.30</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51890827.53601695</t>
+          <t>51846104.14739069</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>25226666</v>
+        <v>46668688.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26250725.0</t>
+          <t>37930663.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>22382197.58</v>
+        <v>24467742.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1024059</t>
+          <t>8738025</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>350649.3172858583</t>
+          <t>1714671.560914318</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1377500.007797588</t>
+          <t>9216793.900870845</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>26830670.0</t>
+          <t>132621113.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>679.114</t>
+          <t>552.397</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-32.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.03</t>
+          <t>-25.84</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.74</v>
+        <v>-0.18</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="AN2" t="n">
         <v>19.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>25842361</v>
+        <v>21535001.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>35556247.8</t>
+          <t>32087340.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>28321904.7</v>
+        <v>28151621.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9713886</t>
+          <t>-10552339</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1568915.175022517</t>
+          <t>778298.7108075505</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2392550.842481308</t>
+          <t>-3570091.842374764</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,243 +1451,243 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>51796149.4943662</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>10366</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>51846104.14739069</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.06</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>30.17</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>10340</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,48 +1873,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AN4" t="n">
         <v>19.7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0.2</v>
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,168 +2280,168 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>51796149.4943662</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>51846104.14739069</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,38 +3103,38 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AM7" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AN7" t="n">
         <v>19.68</v>
       </c>
-      <c r="AN7" t="n">
-        <v>19.67</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,19 +3440,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>-1.52</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,87 +3525,87 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,17 +4390,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.34</v>
+        <v>4.73</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2221.352</t>
+          <t>1781.106</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.20</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.03</t>
+          <t>-23.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>93.14</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.7</v>
+        <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.28</v>
+        <v>4.34</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.38</v>
+        <v>19.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.61</v>
+        <v>19.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>632.62</t>
+          <t>1213.70</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.60</t>
+          <t>-99.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>52593005.4</v>
+        <v>56956798.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>39782194.8</t>
+          <t>40418289.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25031853.16</v>
+        <v>25505320.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>12810810</t>
+          <t>16538509</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2673628.532850632</t>
+          <t>3209958.280239535</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>7947891.878500357</t>
+          <t>6159771.890878506</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>45607941.0</t>
+          <t>36258724.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6307.505</t>
+          <t>2221.352</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>32.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.03</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>552</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.23</v>
+        <v>3.28</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.01</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.32</v>
+        <v>19.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.6</v>
+        <v>19.61</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>211.54</t>
+          <t>632.62</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-101.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>51846104.14739069</t>
+          <t>51796149.4943662</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>46668688.8</v>
+        <v>52593005.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>37930663.3</t>
+          <t>39782194.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>24467742.9</v>
+        <v>25031853.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8738025</t>
+          <t>12810810</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1714671.560914318</t>
+          <t>2673628.532850632</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9216793.900870845</t>
+          <t>7947891.878500357</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>132621113.0</t>
+          <t>45607941.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1214.399</t>
+          <t>3742.489</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-36.29</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,63 +1094,63 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>20</v>
+        <v>20.02</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.7</v>
+        <v>19.72</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.16</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-90.68</t>
+          <t>-90.95</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>19695075.2</v>
+        <v>30947230.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>30912220.5</t>
+          <t>30118556.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>28318662.7</v>
+        <v>29575632.28</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-11217145</t>
+          <t>828674</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>153026.7712616485</t>
+          <t>274833.054676622</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-3285968.896240812</t>
+          <t>944767.6134589761</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>552.397</t>
+          <t>1214.399</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.89</t>
+          <t>-36.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.84</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,266 +1556,266 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.18</v>
+        <v>-0.38</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>19.98</v>
+        <v>20</v>
       </c>
       <c r="AV3" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>-29.31</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-90.68</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>51864863.39957865</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>19695075.2</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>30912220.5</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>28318662.7</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-11217145</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>153026.7712616485</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-3285968.896240812</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>30.49</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>-32.18</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-90.00</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>51775003.41561182</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="n">
-        <v>21535001.4</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>32087340.4</t>
-        </is>
-      </c>
-      <c r="BH3" t="n">
-        <v>28151621.76</v>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-10552339</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>778298.7108075505</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-3570091.842374764</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>679.114</t>
+          <t>552.397</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,142 +1872,142 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-32.89</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-25.84</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-26.03</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.74</v>
+        <v>-0.18</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="AV4" t="n">
         <v>19.69</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>25842361</v>
+        <v>21535001.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>35556247.8</t>
+          <t>32087340.4</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>28321904.7</v>
+        <v>28151621.76</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-9713886</t>
+          <t>-10552339</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1568915.175022517</t>
+          <t>778298.7108075505</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-2392550.842481308</t>
+          <t>-3570091.842374764</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,12 +2480,12 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2495,243 +2495,243 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AV5" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>51864863.39957865</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>30.49</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>51775003.41561182</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="BH5" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CN5" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AV6" t="n">
         <v>19.7</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.2</v>
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,168 +3404,168 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>51864863.39957865</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>51775003.41561182</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BF7" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="BH7" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,42 +3695,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-2.18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1665.664</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1575.957</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20.65</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.74</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,43 +4302,43 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4347,47 +4347,47 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AU9" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AV9" t="n">
         <v>19.68</v>
       </c>
-      <c r="AV9" t="n">
-        <v>19.67</v>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,92 +4764,92 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AV10" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AV11" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1781.106</t>
+          <t>4087.718</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,17 +5714,17 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5733,47 +5733,47 @@
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.15</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.34</v>
+        <v>4.73</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>19.43</v>
+        <v>19.51</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.62</v>
+        <v>19.64</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1213.70</t>
+          <t>304.10</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-99.21</t>
+          <t>-96.73</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>51775003.41561182</t>
+          <t>51864863.39957865</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>56956798.6</v>
+        <v>65285059.2</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>40418289.0</t>
+          <t>44773501.3</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>25505320.52</v>
+        <v>26980928.86</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>16538509</t>
+          <t>20511557</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>3209958.280239535</t>
+          <t>4011149.760552105</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>6159771.890878506</t>
+          <t>8417702.902271241</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>36258724.0</t>
+          <t>85106848.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>11.76</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-0.45</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>40.74</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>2.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-0.93</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>19.99</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>20.02</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>19.72</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-11.85</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.16</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-90.95</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>77170208.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>30947230.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>30118556.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>29575632.28</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>828674</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>274833.054676622</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>944767.6134589761</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>77170208.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>20.95</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>20.45</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>3.82</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-0.49</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>38.89</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>14.81</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-0.38</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-1.15</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>19.92</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>20</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>19.7</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>19.93</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-29.31</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.11</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.16</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-90.68</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>24507525.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>19695075.2</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>30912220.5</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>28318662.7</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-11217145</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>153026.7712616485</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-3285968.896240812</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>24507525.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>20.1</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-1.30</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>19.94</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>19.98</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>19.69</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-32.18</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.12</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.17</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-90.00</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>10918867.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>21535001.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>32087340.4</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>28151621.76</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-10552339</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>778298.7108075505</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-3570091.842374764</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>10918867.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-2.94</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>2.13</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.01</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-1.79</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>0.74</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-1.45</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>20.11</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>19.96</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>19.69</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>19.98</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-19.43</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.15</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.19</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-89.19</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>13454630.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>25842361</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>35556247.8</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>28321904.7</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-9713886</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>1568915.175022517</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-2392550.842481308</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>13454630.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-3.19</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>19.75</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4.54</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.25</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>8.33</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-1.93</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-1.51</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>20.24</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>19.94</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>19.7</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.2</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.2</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-88.67</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>28684924.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>28518363.2</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>47472896.1</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>28662192.12</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-18954532</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>2289181.723659576</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-896590.0625448972</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>28684924.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-2.70</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>19.7</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>19.85</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>3.27</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-0.49</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>41.67</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>2.51</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-1.57</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>20.39</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>19.89</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>19.7</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>20.01</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>22.89</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.24</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.2</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-88.67</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>20909430.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>29289882.2</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>47287470.7</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>28319853.34</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-17997588</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>2868412.957514935</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-359299.3746877089</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>20909430.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>20.1</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>5.24</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-1.48</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>69.95</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-1.46</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>3.39</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-1.64</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>19.83</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>19.69</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>20.02</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>45.63</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.18</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-89.32</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>33707156.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>42129365.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>49543082.2</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>28097779.14</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-7413716</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>3455269.745188142</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>1254179.514204264</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>33707156.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-0.98</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>20.65</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>20.65</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>4.95</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>93.94</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.63</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>3.81</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-1.74</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>20.52</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>19.77</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>19.68</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>20.03</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>77.74</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.29</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.16</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-90.54</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>32455665.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>42639679.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>47616342.4</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>27712944.14</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-4976663</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>3855467.969003393</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>2143172.30139979</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>32455665.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>20.55</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>20.7</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>20.65</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.73</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>84.85</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>93.94</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>4.17</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>0.07</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-1.93</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>19.68</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>19.67</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>103.71</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.13</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-92.38</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>26834641.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>45270134.6</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>45969411.7</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>27411404.62</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-699277</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>4166794.45402223</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>3470708.450914837</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>26834641.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>4.97</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.48</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>96.97</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>93.11</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.29</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>4.84</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.03</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>20.54</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>19.59</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>19.66</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>20.07</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>168.05</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.26</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-94.35</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>32542519.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>66427429</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>45827047.5</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>27251457.28</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>20600381</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>4293355.545496301</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>5845487.362689376</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>32542519.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>20.85</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>20.45</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/08/28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/06/23</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>21.25</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>12.85</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-1.19</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>3742</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>93.14</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>1.08</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>4.73</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-0.7</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-2.15</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>20.43</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>19.51</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>19.64</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>20.08</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>304.10</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.23</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.06</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-96.73</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>51864863.39957865</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>85106848.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>65285059.2</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>44773501.3</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>26980928.86</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>20511557</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>4011149.760552105</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>8417702.902271241</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>85106848.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/12/03</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>允強</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-42.75264470335272</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-9.218241067287693</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>5.64</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>12.63%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>5.61%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>10707</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>允強-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>鋼鐵工業右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>21.2</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>20.65</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>18.1</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 冷熱軋不鏽鋼板捲、不鏽鋼型鋼、裁剪加工、製管</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3742.489</t>
+          <t>1543.705</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>20.02</v>
+        <v>20.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-91.29</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>30947230.8</v>
+        <v>31446132.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>30118556.5</t>
+          <t>29982247.8</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>29575632.28</v>
+        <v>29367567.7</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>828674</t>
+          <t>1463884</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>274833.054676622</t>
+          <t>299221.1662513487</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>944767.6134589761</t>
+          <t>433355.7799123451</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1214.399</t>
+          <t>3742.489</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-36.29</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>20</v>
+        <v>20.02</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.7</v>
+        <v>19.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BD3" t="n">
         <v>0.16</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-90.68</t>
+          <t>-90.95</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>19695075.2</v>
+        <v>30947230.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>30912220.5</t>
+          <t>30118556.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>28318662.7</v>
+        <v>29575632.28</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-11217145</t>
+          <t>828674</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>153026.7712616485</t>
+          <t>274833.054676622</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3285968.896240812</t>
+          <t>944767.6134589761</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>552.397</t>
+          <t>1214.399</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-32.89</t>
+          <t>-36.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.84</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,266 +2098,266 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.18</v>
+        <v>-0.38</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>19.98</v>
+        <v>20</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-29.31</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-90.68</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>51857716.53366059</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>19695075.2</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>30912220.5</t>
+        </is>
+      </c>
+      <c r="BL4" t="n">
+        <v>28318662.7</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-11217145</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>153026.7712616485</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-3285968.896240812</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>30.14</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>10523</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-32.18</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-90.00</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>51864863.39957865</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>21535001.4</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>32087340.4</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>28151621.76</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-10552339</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>778298.7108075505</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-3570091.842374764</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>30.49</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>10707</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>679.114</t>
+          <t>552.397</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,149 +2404,149 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-32.89</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-25.84</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
           <t>19.75</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-26.03</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>2025/10/31</t>
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.74</v>
+        <v>-0.18</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="AZ5" t="n">
         <v>19.69</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>25842361</v>
+        <v>21535001.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>35556247.8</t>
+          <t>32087340.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>28321904.7</v>
+        <v>28151621.76</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-9713886</t>
+          <t>-10552339</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1568915.175022517</t>
+          <t>778298.7108075505</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2392550.842481308</t>
+          <t>-3570091.842374764</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,243 +3077,243 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51857716.53366059</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="BL6" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>30.14</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>10523</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>51864863.39957865</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>30.49</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>10707</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CR6" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,48 +3559,48 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AZ7" t="n">
         <v>19.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="BD7" t="n">
         <v>0.2</v>
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,168 +4026,168 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51857716.53366059</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>51864863.39957865</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="BZ8" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,38 +4969,38 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AY10" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>19.68</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>19.67</v>
-      </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,232 +5306,232 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.62</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-23.60</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>-0.73</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-22.85</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>4.97</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>-0.48</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4087.718</t>
+          <t>1580.465</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>93.14</t>
+          <t>93.11</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>19.51</v>
+        <v>19.59</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.64</v>
+        <v>19.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>304.10</t>
+          <t>168.05</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-96.73</t>
+          <t>-94.35</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51864863.39957865</t>
+          <t>51857716.53366059</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>65285059.2</v>
+        <v>66427429</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>44773501.3</t>
+          <t>45827047.5</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>26980928.86</v>
+        <v>27251457.28</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>20511557</t>
+          <t>20600381</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>4011149.760552105</t>
+          <t>4293355.545496301</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>8417702.902271241</t>
+          <t>5845487.362689376</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>85106848.0</t>
+          <t>32542519.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1543.705</t>
+          <t>1202.128</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,61 +1139,61 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>57.94</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.73</v>
+        <v>19.75</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-91.29</t>
+          <t>-91.63</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>31179432.0</t>
+          <t>24336796.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>31446132.4</v>
+        <v>33622565.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>29982247.8</t>
+          <t>29732463.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>29367567.7</v>
+        <v>29470781.78</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1463884</t>
+          <t>3890102</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>299221.1662513487</t>
+          <t>184161.894817588</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>433355.7799123451</t>
+          <t>-448664.0980680957</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>31179432.0</t>
+          <t>24336796.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3742.489</t>
+          <t>1543.705</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,162 +1450,162 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-24.72</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>-1.74</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-23.41</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>11.76</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>-0.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>20.02</v>
+        <v>20.06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-91.29</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>30947230.8</v>
+        <v>31446132.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>30118556.5</t>
+          <t>29982247.8</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>29575632.28</v>
+        <v>29367567.7</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>828674</t>
+          <t>1463884</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>274833.054676622</t>
+          <t>299221.1662513487</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>944767.6134589761</t>
+          <t>433355.7799123451</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1214.399</t>
+          <t>3742.489</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.29</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,58 +2103,58 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>20</v>
+        <v>20.02</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.7</v>
+        <v>19.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BD4" t="n">
         <v>0.16</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-90.68</t>
+          <t>-90.95</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>19695075.2</v>
+        <v>30947230.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>30912220.5</t>
+          <t>30118556.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>28318662.7</v>
+        <v>29575632.28</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-11217145</t>
+          <t>828674</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>153026.7712616485</t>
+          <t>274833.054676622</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3285968.896240812</t>
+          <t>944767.6134589761</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,42 +2389,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1214.399</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>552.397</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.89</t>
+          <t>-36.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.84</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,261 +2585,261 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.18</v>
+        <v>-0.38</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>19.98</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-29.31</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>-90.68</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>51836214.4012605</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>19695075.2</v>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>30912220.5</t>
+        </is>
+      </c>
+      <c r="BL5" t="n">
+        <v>28318662.7</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-11217145</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>153026.7712616485</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-3285968.896240812</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>10549</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-32.18</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-90.00</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>51857716.53366059</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>21535001.4</v>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>32087340.4</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
-        <v>28151621.76</v>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-10552339</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>778298.7108075505</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-3570091.842374764</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>30.14</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>679.114</t>
+          <t>552.397</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,172 +2886,172 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-32.89</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-25.84</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>19.75</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-26.03</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.74</v>
+        <v>-0.18</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="AZ6" t="n">
         <v>19.69</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>25842361</v>
+        <v>21535001.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>35556247.8</t>
+          <t>32087340.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>28321904.7</v>
+        <v>28151621.76</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-9713886</t>
+          <t>-10552339</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1568915.175022517</t>
+          <t>778298.7108075505</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2392550.842481308</t>
+          <t>-3570091.842374764</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,243 +3559,243 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>51836214.4012605</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="BL7" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>10549</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>51857716.53366059</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="BL7" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ7" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>30.14</t>
-        </is>
-      </c>
-      <c r="CL7" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="CM7" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN7" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CR7" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,48 +4041,48 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AZ8" t="n">
         <v>19.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="BD8" t="n">
         <v>0.2</v>
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,163 +4513,163 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>51836214.4012605</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="BL9" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>51857716.53366059</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="BZ9" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,22 +5451,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr"/>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AY11" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>19.68</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>19.67</v>
-      </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1580.465</t>
+          <t>1314.256</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.85</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,22 +5933,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr"/>
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>93.11</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.84</v>
+        <v>4.17</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>19.59</v>
+        <v>19.68</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.66</v>
+        <v>19.67</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>168.05</t>
+          <t>103.71</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-94.35</t>
+          <t>-92.38</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51857716.53366059</t>
+          <t>51836214.4012605</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>66427429</v>
+        <v>45270134.6</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>45827047.5</t>
+          <t>45969411.7</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>27251457.28</v>
+        <v>27411404.62</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>20600381</t>
+          <t>-699277</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>4293355.545496301</t>
+          <t>4166794.45402223</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>5845487.362689376</t>
+          <t>3470708.450914837</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>32542519.0</t>
+          <t>26834641.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1202.128</t>
+          <t>1241.905</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,59 +1134,59 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>53.44</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>20.12</v>
+        <v>20.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.75</v>
+        <v>19.77</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.84</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>-14.54</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-91.63</t>
+          <t>-91.92</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>24336796.0</t>
+          <t>25220488.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>33622565.6</v>
+        <v>36482889.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>29732463.3</t>
+          <t>29008945.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>29470781.78</v>
+        <v>29704829.1</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3890102</t>
+          <t>7473944</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>184161.894817588</t>
+          <t>3739.370968312578</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-448664.0980680957</t>
+          <t>-988584.5102027021</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>24336796.0</t>
+          <t>25220488.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1543.705</t>
+          <t>1202.128</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-24.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>57.94</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>20.12</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>20.06</v>
+        <v>20.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.73</v>
+        <v>19.75</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-91.29</t>
+          <t>-91.63</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>31179432.0</t>
+          <t>24336796.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>31446132.4</v>
+        <v>33622565.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>29982247.8</t>
+          <t>29732463.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>29367567.7</v>
+        <v>29470781.78</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1463884</t>
+          <t>3890102</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>299221.1662513487</t>
+          <t>184161.894817588</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>433355.7799123451</t>
+          <t>-448664.0980680957</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>31179432.0</t>
+          <t>24336796.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3742.489</t>
+          <t>1543.705</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>20.02</v>
+        <v>20.06</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.72</v>
+        <v>19.73</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11.85</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-91.29</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>30947230.8</v>
+        <v>31446132.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>30118556.5</t>
+          <t>29982247.8</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>29575632.28</v>
+        <v>29367567.7</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>828674</t>
+          <t>1463884</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>274833.054676622</t>
+          <t>299221.1662513487</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>944767.6134589761</t>
+          <t>433355.7799123451</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>77170208.0</t>
+          <t>31179432.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1214.399</t>
+          <t>3742.489</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.29</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,63 +2580,63 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>20.02</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.7</v>
+        <v>19.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-11.85</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BD5" t="n">
         <v>0.16</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-90.68</t>
+          <t>-90.95</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>19695075.2</v>
+        <v>30947230.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>30912220.5</t>
+          <t>30118556.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>28318662.7</v>
+        <v>29575632.28</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-11217145</t>
+          <t>828674</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>153026.7712616485</t>
+          <t>274833.054676622</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3285968.896240812</t>
+          <t>944767.6134589761</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>24507525.0</t>
+          <t>77170208.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>552.397</t>
+          <t>1214.399</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.89</t>
+          <t>-36.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.84</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,266 +3062,266 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.18</v>
+        <v>-0.38</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>19.98</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
+          <t>19.93</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-29.31</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-90.68</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>51816626.31398602</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>19695075.2</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>30912220.5</t>
+        </is>
+      </c>
+      <c r="BL6" t="n">
+        <v>28318662.7</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-11217145</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>153026.7712616485</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-3285968.896240812</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>24507525.0</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>29.98</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
           <t>19.95</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-32.18</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-90.00</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>51836214.4012605</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="n">
-        <v>21535001.4</v>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>32087340.4</t>
-        </is>
-      </c>
-      <c r="BL6" t="n">
-        <v>28151621.76</v>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-10552339</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>778298.7108075505</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-3570091.842374764</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>10918867.0</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>10549</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>679.114</t>
+          <t>552.397</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,149 +3368,149 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-32.89</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2024-07-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>26.65</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>25.25</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-25.84</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5.54</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/06/23</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>19.75</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2024-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2024-07-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>26.65</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-26.03</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/06/23</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>2025/10/31</t>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.74</v>
+        <v>-0.18</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>19.96</v>
+        <v>19.98</v>
       </c>
       <c r="AZ7" t="n">
         <v>19.69</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-19.43</t>
+          <t>-32.18</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-89.19</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>25842361</v>
+        <v>21535001.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>35556247.8</t>
+          <t>32087340.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>28321904.7</v>
+        <v>28151621.76</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-9713886</t>
+          <t>-10552339</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1568915.175022517</t>
+          <t>778298.7108075505</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2392550.842481308</t>
+          <t>-3570091.842374764</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>13454630.0</t>
+          <t>10918867.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1444.662</t>
+          <t>679.114</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.93</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.66</t>
+          <t>-26.03</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,243 +4041,243 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-1.93</v>
+        <v>-1.79</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.52</v>
+        <v>0.74</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>19.94</v>
+        <v>19.96</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.7</v>
+        <v>19.69</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-19.43</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>-89.19</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>51816626.31398602</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>25842361</v>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>35556247.8</t>
+        </is>
+      </c>
+      <c r="BL8" t="n">
+        <v>28321904.7</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-9713886</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>1568915.175022517</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-2392550.842481308</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>13454630.0</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-3.19</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>-24.01869676127416</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>-42.75264470335272</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>-9.218241067287693</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>12.63%</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>5.61%</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>29.98</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>允強-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-88.67</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>51836214.4012605</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="n">
-        <v>28518363.2</v>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>47472896.1</t>
-        </is>
-      </c>
-      <c r="BL8" t="n">
-        <v>28662192.12</v>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-18954532</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>2289181.723659576</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-896590.0625448972</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>28684924.0</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>-24.01869676127416</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>-42.75264470335272</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>-9.218241067287693</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>12.63%</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>5.61%</t>
-        </is>
-      </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="CL8" t="inlineStr">
-        <is>
-          <t>10549</t>
-        </is>
-      </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>不�袗�管58.36%、不�袗�板/捲39.97%、其他不�袗�製品及其他營業1.67% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>允強-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>20.05</t>
-        </is>
-      </c>
       <c r="CR8" t="inlineStr">
         <is>
           <t>19.7</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1041.67</t>
+          <t>1444.662</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-39.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-25.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,48 +4523,48 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-1.42</v>
+        <v>-1.93</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="AZ9" t="n">
         <v>19.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="BD9" t="n">
         <v>0.2</v>
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>29289882.2</v>
+        <v>28518363.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>47287470.7</t>
+          <t>47472896.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>28319853.34</v>
+        <v>28662192.12</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-17997588</t>
+          <t>-18954532</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2868412.957514935</t>
+          <t>2289181.723659576</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-359299.3746877089</t>
+          <t>-896590.0625448972</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>20909430.0</t>
+          <t>28684924.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1665.664</t>
+          <t>1041.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-38.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,168 +4990,168 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>22.89</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-88.67</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>51816626.31398602</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>29289882.2</v>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>47287470.7</t>
+        </is>
+      </c>
+      <c r="BL10" t="n">
+        <v>28319853.34</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-17997588</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>2868412.957514935</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-359299.3746877089</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>20909430.0</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2025/12/03</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>允強</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>19.83</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-89.32</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>51836214.4012605</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
-        <v>42129365.8</v>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>49543082.2</t>
-        </is>
-      </c>
-      <c r="BL10" t="n">
-        <v>28097779.14</v>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-7413716</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>3455269.745188142</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>1254179.514204264</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>33707156.0</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2025/12/03</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>允強</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
       <c r="BZ10" t="inlineStr">
         <is>
           <t>-24.01869676127416</t>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1575.957</t>
+          <t>1665.664</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.66</t>
+          <t>-24.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>69.95</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.63</v>
+        <v>-1.46</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>19.77</v>
+        <v>19.83</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19.68</v>
+        <v>19.69</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-90.54</t>
+          <t>-89.32</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>42639679.4</v>
+        <v>42129365.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>47616342.4</t>
+          <t>49543082.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>27712944.14</v>
+        <v>28097779.14</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-4976663</t>
+          <t>-7413716</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>3855467.969003393</t>
+          <t>3455269.745188142</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>2143172.30139979</t>
+          <t>1254179.514204264</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>32455665.0</t>
+          <t>33707156.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1314.256</t>
+          <t>1575.957</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-22.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,38 +5933,38 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5973,47 +5973,47 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.52</t>
         </is>
       </c>
       <c r="AY12" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>19.68</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>19.67</v>
-      </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>77.74</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-92.38</t>
+          <t>-90.54</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51836214.4012605</t>
+          <t>51816626.31398602</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>45270134.6</v>
+        <v>42639679.4</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>45969411.7</t>
+          <t>47616342.4</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>27411404.62</v>
+        <v>27712944.14</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-699277</t>
+          <t>-4976663</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>4166794.45402223</t>
+          <t>3855467.969003393</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>3470708.450914837</t>
+          <t>2143172.30139979</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>26834641.0</t>
+          <t>32455665.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/不鏽鋼型鋼.xlsx
+++ b/Result/checksun_type/不鏽鋼型鋼.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>948.753</t>
+          <t>812.311</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.78</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,38 +1144,38 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>812</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>69.05</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.49</v>
+        <v>0.99</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1184,23 +1184,23 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>20.24</v>
+        <v>20.26</v>
       </c>
       <c r="BA2" t="n">
-        <v>19.79</v>
+        <v>19.8</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="BE2" t="n">
         <v>0.14</v>
@@ -1212,53 +1212,53 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-92.05</t>
+          <t>-92.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>51784758.67248604</t>
+          <t>51747250.5209205</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>19332930.0</t>
+          <t>16594276.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>35447970.8</v>
+        <v>23332784.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>27571523.0</t>
+          <t>27140007.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>29884374.86</v>
+        <v>29890310.52</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>7876447</t>
+          <t>-3807223</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-271202.2300947912</t>
+          <t>-614179.29132032</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-1783381.035941862</t>
+          <t>-2500553.128060728</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>19332930.0</t>
+          <t>16594276.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1241.905</t>
+          <t>948.753</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.34</t>
+          <t>-23.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,63 +1631,63 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>812</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>53.44</t>
+          <t>69.05</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>20.17</v>
+        <v>20.24</v>
       </c>
       <c r="BA3" t="n">
-        <v>19.77</v>
+        <v>19.79</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-14.54</t>
+          <t>-6.52</t>
         </is>
       </